--- a/backend/nice.xlsx
+++ b/backend/nice.xlsx
@@ -11,7 +11,7 @@
     <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$C$1:$C$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$D$1:$D$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="143">
   <si>
     <t>年级</t>
   </si>
@@ -566,86 +566,6 @@
     <t>3+23+35=
 48-24-6=
 34+（45-33）=</t>
-  </si>
-  <si>
-    <t>竖式计算</t>
-  </si>
-  <si>
-    <t>\[
-\begin{array}{@{}c@{}c@{}c}
-  &amp; 3 &amp; 5 \\
-+ &amp; 3 &amp; 2 \\
-\cline{2-3}
-  &amp;   &amp;   \\
-\end{array}
-\]</t>
-  </si>
-  <si>
-    <t>\[
-\begin{array}{@{}c@{}c@{}c}
-  &amp; 3 &amp; 5 \\
-+ &amp; 3 &amp; 7 \\
-\cline{2-3}
-  &amp;   &amp;   \\
-\end{array}
-\]</t>
-  </si>
-  <si>
-    <t>\[
-\begin{array}{@{}c@{}c@{}c}
-  &amp; 3 &amp; 8 \\
-- &amp; 2 &amp; 2 \\
-\cline{2-3}
-  &amp;   &amp;   \\
-\end{array}
-\]</t>
-  </si>
-  <si>
-    <t>\[
-\begin{array}{@{}c@{}c@{}c}
-  &amp; 3 &amp; 5 \\
-- &amp; 1 &amp; 7 \\
-\cline{2-3}
-  &amp;   &amp;   \\
-\end{array}
-\]</t>
-  </si>
-  <si>
-    <t>\[
-\begin{array}{@{}c@{}c@{}c}
-  &amp; 3 &amp; 5 \\
-+ &amp; 3 &amp; 2 \\
-\cline{2-3}
-  &amp;   &amp;   \\
-\end{array}
-\]
-\[
-\begin{array}{@{}c@{}c@{}c}
-  &amp; 3 &amp; 5 \\
-+ &amp; 3 &amp; 7 \\
-\cline{2-3}
-  &amp;   &amp;   \\
-\end{array}
-\]
-\[
-\begin{array}{@{}c@{}c@{}c}
-  &amp; 3 &amp; 8 \\
-- &amp; 2 &amp; 2 \\
-\cline{2-3}
-  &amp;   &amp;   \\
-\end{array}
-\]
-\[
-\begin{array}{@{}c@{}c@{}c}
-  &amp; 3 &amp; 8 \\
-- &amp; 2 &amp; 2 \\
-\cline{2-3}
-  &amp;   &amp;   \\
-\end{array}
-\]</t>
-  </si>
-  <si>
-    <t>单位换算</t>
   </si>
   <si>
     <t>元、角、分</t>
@@ -1450,14 +1370,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1972,7 +1892,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.9416666666667" customWidth="1"/>
@@ -3363,7 +3283,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="61" ht="132" spans="1:7">
+    <row r="61" ht="66" spans="1:7">
       <c r="A61" s="3" t="s">
         <v>7</v>
       </c>
@@ -3374,19 +3294,19 @@
         <v>9</v>
       </c>
       <c r="D61" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="F61" s="3" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="62" ht="132" spans="1:7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="62" ht="148.5" spans="1:7">
       <c r="A62" s="3" t="s">
         <v>7</v>
       </c>
@@ -3397,19 +3317,19 @@
         <v>9</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="F62" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="63" ht="132" spans="1:7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="63" ht="66" spans="1:7">
       <c r="A63" s="3" t="s">
         <v>7</v>
       </c>
@@ -3420,152 +3340,37 @@
         <v>9</v>
       </c>
       <c r="D63" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E63" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="64" ht="132" spans="1:7">
-      <c r="A64" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="65" ht="409.5" spans="1:7">
-      <c r="A65" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="G65" s="12" t="s">
+      <c r="F63" s="12" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="66" ht="66" spans="1:7">
-      <c r="A66" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="3" t="s">
+      <c r="G63" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="67" ht="148.5" spans="1:7">
-      <c r="A67" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="68" ht="66" spans="1:7">
-      <c r="A68" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G68" s="12" t="s">
-        <v>141</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:C68" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="D1:D63" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <dataValidations count="21">
+  <dataValidations count="19">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F58">
       <formula1>"期末复习,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D61 D62 D63 D2:D60">
+      <formula1>"口算练习,竖式计算,单位换算,知识运用,"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A60 A61:A63">
       <formula1>"一年级,二年级,三年级,四年级,五年级,六年级,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B60 B61:B63">
       <formula1>"上学期,下学期,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C60 C61:C63">
       <formula1>"人教版（2024新版）,北师大（2024新版）,苏教版（2024新版）,青岛六三版（2024新版）,冀教版（2024新版）,青岛五四版（2024新版）,沪教版（2024新版）,北京版（2024新版）,西南大学版,人教版,北师大,苏教版,西师版,浙教版,青岛六三版,沪教版,冀教版,北京版,青岛五四版,"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D68">
-      <formula1>"口算练习,竖式计算,单位换算,知识运用,"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E33">
       <formula1>"5以内数的认识和加、减法,6~10的认识和加、减法,11~20各数的认识,20以内的进位加法,复习与关练,专项练习,"</formula1>
@@ -3573,10 +3378,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E34:E60">
       <formula1>"20以内的退位减法,100以内数的认识,100以内的口算加、减法,100以内的笔算加、减法,期末复习,专项练习,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E61:E65">
-      <formula1>"100以内的笔算加、减法,"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E66:E68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E61:E63">
       <formula1>"元、角、分,期末复习,"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6">
@@ -3609,10 +3411,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F59:F60">
       <formula1>"100以内的进位加法和退位减法,100以内的连加连减、加减混合,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F61:F65">
-      <formula1>"两位数加两位数（不进位）,两位数加两位数（进位）,两位数减两位数（不退位）,两位数减两位数（退位）,单元综合练习,"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F66:F68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F61:F63">
       <formula1>"元、角、分（比大小）,元、角、分（换算）,元、角、分（计算）,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3635,13 +3434,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -3670,7 +3469,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:7">
@@ -3762,7 +3561,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:7">
@@ -3808,7 +3607,7 @@
         <v>25</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:7">
@@ -3851,7 +3650,7 @@
         <v>22</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>30</v>
@@ -3877,7 +3676,7 @@
         <v>31</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:7">
@@ -3946,7 +3745,7 @@
         <v>37</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:7">
